--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0043.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0043.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Cube Được Hỗ Trợ</t>
+          <t>Hỗ Trợ Khối</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Cube Ranking</t>
+          <t>Bảng Xếp Hạng Khối</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Popularity Changes</t>
+          <t>Biến động độ nổi tiếng</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Không Hỗ Trợ Record</t>
+          <t>Không có Hồ sơ Hỗ trợ</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Ranking</t>
+          <t>Xếp hạng</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Tên</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Correct Predictions</t>
+          <t>Dự đoán chính xác</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Total Popularity</t>
+          <t>Tổng Độ Phổ Biến</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Not on the Board</t>
+          <t>Không có trên bảng</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Daily Tasks</t>
+          <t>Nhiệm Vụ Hằng Ngày</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Đạt 100 điểm Hoạt động Sổ tay Hướng dẫn</t>
+          <t>Thu thập 100 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Đang Tiến Hành</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Champion</t>
+          <t>Quán Quân</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Rewards hỗ trợ</t>
+          <t>Phần Thưởng Hỗ Trợ</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Rewards độ phổ biến</t>
+          <t>Phần thưởng độ nổi tiếng</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Hỗ trợ một Cube và xác nhận kết quả 1 trận trong trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả của 1 trận đấu trên trang sự kiện</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Hỗ trợ một Cube và xác nhận kết quả 2 trận trong trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 2 trận trên trang sự kiện</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Hỗ trợ một Cube và xác nhận kết quả 3 trận trong trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 3 trận trên trang sự kiện</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Hỗ trợ một Cube và xác nhận kết quả 4 trận trong trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 4 trận trên trang sự kiện</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Ủng hộ một Cube và xác nhận kết quả 5 trận trong trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 5 trận trên trang sự kiện</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Ủng hộ một Cube và xác nhận kết quả 6 trận trong trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 6 trận trên trang sự kiện</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Ủng hộ một Cube và xác nhận kết quả 7 trận trong trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 7 trận trên trang sự kiện</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Ủng hộ một Cube và xác nhận kết quả 8 trận trong trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 8 trận đấu trên trang sự kiện</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Ủng hộ một Cube và xác nhận kết quả 9 trận trong trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 9 trận đấu trên trang sự kiện</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Ủng hộ một Cube và xác nhận kết quả 10 trận trong trang sự kiện</t>
+          <t>Ủng hộ một Khối Lập Phương và xác nhận kết quả 10 trận trên trang sự kiện</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Nhận 2.000 điểm Uy tín thông qua Ủng hộ</t>
+          <t>Nhận 2.000 Điểm Phổ Biến qua Hỗ Trợ.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Nhận 3.500 điểm Uy tín thông qua Ủng hộ</t>
+          <t>Đạt 3.500 điểm Phổ Biến qua Hỗ Trợ.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Nhận 5.000 điểm Uy tín thông qua Ủng hộ</t>
+          <t>Thu thập 5.000 Điểm Phổ Biến qua Hỗ Trợ</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Nhận 7.500 điểm Uy tín thông qua Ủng hộ</t>
+          <t>Đạt 7.500 điểm Phổ Biến thông qua Hỗ Trợ</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Nhận 10.000 điểm Uy tín thông qua Ủng hộ</t>
+          <t>Nhận 10.000 Điểm Phổ Biến qua Hỗ Trợ</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Nhận 15.000 điểm Uy tín thông qua Ủng hộ</t>
+          <t>Đạt 15.000 điểm Nổi Tiếng qua Hỗ Trợ.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Nhận 20.000 điểm Uy tín thông qua Ủng hộ</t>
+          <t>Đạt 20.000 điểm Nổi tiếng qua Hỗ trợ</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Save Complete</t>
+          <t>Đã Lưu Xong</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Saving Available</t>
+          <t>Có thể lưu</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Cube Exclusive</t>
+          <t>Khối Độc Quyền</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Universal Text</t>
+          <t>Văn Bản Chung</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Comment Opacity</t>
+          <t>Độ mờ bình luận</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Display Area</t>
+          <t>Khu vực hiển thị</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>In the Name of the Magistrate</t>
+          <t>Nhân Danh Quan Phán</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Plan Before Acting</t>
+          <t>Hãy lên kế hoạch trước khi hành động</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>One With the Shadows</t>
+          <t>Hòa Nhập Bóng Tối</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Collective Future</t>
+          <t>Tương Lai Tập Thể.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Solo Extravaganza</t>
+          <t>Đại Tiệc Solo</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Double the Profits</t>
+          <t>Lợi Nhuận Gấp Đôi</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Show Time</t>
+          <t>Hiển thị Thời Gian</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Upper Hand</t>
+          <t>Lợi Thế</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Snatch Vậy thì Grab</t>
+          <t>Chộp Rồi Giật</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Overtime To the Left, Vacation To the Right</t>
+          <t>Bên trái là Overtime, bên phải là kỳ nghỉ</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Plot Twist</t>
+          <t>Bất Ngờ Đến Tận Cùng</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>The Sentinel Protects</t>
+          <t>Người Bảo Vệ Canh Gác</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Ground Remains Echo Challenge: Flight</t>
+          <t>Thử thách Tàn tích Echo Mặt đất: Bay lượn</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Treasure Spot Challenge II</t>
+          <t>Thử Thách Điểm Kho Báu II</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Flash Dodge II</t>
+          <t>Né Tia Chớp II</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Cloud Platformer</t>
+          <t>Bậc Thang Mây</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Flash Dodge I</t>
+          <t>Né Tia Chớp I</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Dream Patrol</t>
+          <t>Tuần Tra Giấc Mơ</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Boat Racing I</t>
+          <t>Đua Thuyền I</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Ace Wings II</t>
+          <t>Đôi Cánh Phi Thường II</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Coercitors: The Verdict</t>
+          <t>Các Thi Hành Quan: Phán Quyết</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Đánh bại các sứ giả canh giữ khu vực để chấm dứt thử thách vô nghĩa này…</t>
+          <t>Đánh bại những sứ giả canh giữ khu vực để chấm dứt thử thách vô nghĩa này…</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Resurfaced Past</t>
+          <t>Quá Khứ Trỗi Dậy</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Action Order</t>
+          <t>Lệnh Hành Động</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Current action in progress</t>
+          <t>Đang thực hiện hành động</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Nếu Sao Băng Rực Cháy</t>
+          <t>Nếu Sao Băng Phải Cháy Lên</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Ngõ Tối</t>
+          <t>Black Alley</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>The Match Has Ended</t>
+          <t>Trận Đấu Đã Kết Thúc</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Cubie Derby: Championship hiện đã mở</t>
+          <t>Giải Đua Cubie: Vô Địch đã mở!</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Tarnished Kiếm Tomb</t>
+          <t>Mộ Kiếm Nhơ</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Tarnished Kiếm Tomb</t>
+          <t>Mộ Kiếm Nhơ</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Tarnished Kiếm Tomb</t>
+          <t>Mộ Kiếm Nhơ</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>A Short Poem</t>
+          <t>Một Bài Thơ Ngắn</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Some Notes</t>
+          <t>Vài ghi chú</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Incomplete Log</t>
+          <t>Nhật ký chưa hoàn thiện</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Treasure Spot III</t>
+          <t>Điểm Kho Báu III</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Thermes Baths</t>
+          <t>Suối Nước Nóng Thermes</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Quick Slash Challenge: Gladiator's Spirit I</t>
+          <t>Thử Thách Vung Kiếm Nhanh: Tinh Thần Võ Sĩ I</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Hero's Rend II</t>
+          <t>Phách Anh Hùng II</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Underground Flight Challenge</t>
+          <t>Thử Thách Bay Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Trước đó, bạn và Cartethyia đã đi kiểm tra dấu vết do Fractsidus để lại…</t>
+          <t>Trước đó, cậu và Cartethyia đã đi kiểm tra những dấu vết còn sót lại của Fractsidus…</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Experiment Records</t>
+          <t>Các Biên Bản Thí Nghiệm</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Thử thách Flight Không Đất</t>
+          <t>Thử Thách Bay Không Động Đất</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,8 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>[Thử thách Vung Kiếm Nhanh: Tinh thần Võ sĩ I]</t>
+          <t>[
+Thử Thách Vung Kiếm Nhanh: Tinh Thần Võ Sĩ I]</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6665,8 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>[Thử thách Vung Kiếm Nhanh: Tinh thần Võ sĩ II]</t>
+          <t>[
+Thử Thách Vung Kiếm Nhanh: Tinh Thần Võ Sĩ II]</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6736,8 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>[Thử thách Vung Kiếm Nhanh: Tinh thần Võ sĩ III]</t>
+          <t>[
+Thử Thách Vung Kiếm Nhanh: Tinh Thần Võ Sĩ III]</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6807,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Nơi Bầu Trời Trong Xanh và Glory Chói Lọi: Tower Bảo Vệ</t>
+          <t>Nơi Trời Quang Vinh Quang Chói Lọi: Tháp Canh Giám Hộ</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6877,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Flames in the Deep</t>
+          <t>Lửa Trong Vực Sâu</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6947,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Thử thách Flight Dưới Lòng Đất</t>
+          <t>Thử Thách Bay Dưới Lòng Đất</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7017,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Đánh bại Kerasaur bị phong ấn tại Titanbone Expanse</t>
+          <t>Tiêu diệt Kerasaur bị phong ấn trên Titanbone Expanse</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7087,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Trước đó, bạn và Cartethyia đã đi kiểm tra dấu vết do Fractsidus để lại…</t>
+          <t>Trước đó, cậu và Cartethyia đã đi kiểm tra những dấu vết còn sót lại của Fractsidus…</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7157,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Hầm Mộ Dragon Tro - Tầng Trên</t>
+          <t>Hầm Mộ Rồng Tro Tàn - Tầng Trên</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7227,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Hầm Mộ Dragon Tro - Tầng Dưới</t>
+          <t>Hầm Mộ Rồng Tro Tàn - Tầng Dưới</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7297,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Vampire demo level01</t>
+          <t>Màn demo ma cà rồng cấp 01</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7367,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Vampire demo level02</t>
+          <t>Màn thử nghiệm ma cà rồng 02</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7437,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Vampire demo level03</t>
+          <t>Màn thử nghiệm ma cà rồng 03</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7507,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Vampire demo level04</t>
+          <t>Màn thử nghiệm ma cà rồng 04</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7577,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Vampire demo level05</t>
+          <t>Màn thử nghiệm ma cà rồng 05</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7647,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Vampire demo level06</t>
+          <t>Màn thử nghiệm ma cà rồng 06</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7717,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Vampire demo level07</t>
+          <t>Màn thử nghiệm ma cà rồng 07</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7787,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Words Between Melodies</t>
+          <t>Lời Giữa Những Giai Điệu</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7857,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Words Between Melodies</t>
+          <t>Lời Giữa Những Giai Điệu</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7927,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Words Between Melodies</t>
+          <t>Lời Giữa Những Giai Điệu</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7997,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Words Between Melodies</t>
+          <t>Lời Giữa Những Giai Điệu</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8067,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Words Between Melodies</t>
+          <t>Lời Giữa Những Giai Điệu</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8137,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>As if Time Slows</t>
+          <t>Như thể Thời Gian Trôi Chậm</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8207,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Devotee</t>
+          <t>Tín Đồ</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8277,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Sacred Muối Side Up</t>
+          <t>Muối Thiêng Lật Mặt</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8347,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>One Punch Shrimp</t>
+          <t>Tôm Hùm Một Đấm</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8417,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Orchestrator</t>
+          <t>Điều phối viên</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8487,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Lặp Lại Không Ngừng</t>
+          <t>Lặp đi lặp lại</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8557,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Moon in Water</t>
+          <t>Trăng Dưới Nước</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8627,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Ashes to Ashes</t>
+          <t>Tro Bụi Trở Về Tro Bụi</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8697,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Into the Waves</t>
+          <t>Vào Sóng Dữ</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8767,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Polyphone Orchestration</t>
+          <t>Dàn Hòa Âm Đa Âm</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8837,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Triptych Chests</t>
+          <t>Rương Ba Mảnh</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8907,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Pipeline Maintenance</t>
+          <t>Bảo trì Đường ống Năng lượng</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8977,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Dấu Ấn Hoang Dã</t>
+          <t>Dấu Vết Hoang Dã</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9047,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Treasure Spot I</t>
+          <t>Điểm Kho Báu I</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9117,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Treasure Spot II</t>
+          <t>Điểm Kho Báu II</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9187,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Treasure Spot III</t>
+          <t>Điểm Kho Báu III</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9257,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Treasure Spot IV</t>
+          <t>Điểm Kho Báu IV</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9327,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Treasure Spot V</t>
+          <t>Điểm Kho Báu V</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9397,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Treasure Spot VI</t>
+          <t>Điểm Kho Báu VI</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9467,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Treasure Spot VII</t>
+          <t>Điểm Kho Báu VII</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9537,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Treasure Spot VIII</t>
+          <t>Điểm Kho Báu VIII</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9607,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Treasure Spot IX</t>
+          <t>Điểm Kho Báu IX</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9677,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Treasure Spot X</t>
+          <t>Điểm Kho Báu X</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9747,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Treasure Spot XI</t>
+          <t>Điểm Kho Báu XI</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9817,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Treasure Spot XII</t>
+          <t>Điểm Kho Báu XII</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9887,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Shards of the Beyond</t>
+          <t>Mảnh Vực Ngoài</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9957,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Fabricatorium Operations Manual 26</t>
+          <t>Cẩm Nang Vận Hành Fabricatorium 26</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10027,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Fabricatorium Operations Manual 35</t>
+          <t>Cẩm Nang Vận Hành Fabricatorium 35</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10097,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Biên Niên Sử Các Primus Quá Khứ (Tập Một, Trích Đoạn)</t>
+          <t>Biên Niên Sử Các Primus Cổ Xưa (Tập Một, Trích Đoạn)</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10167,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Lịch Sử Rinascita (Trích Đoạn 1)</t>
+          <t>Lịch sử Rinascita (Trích đoạn 1)</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10237,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Lịch Sử Rinascita (Trích Đoạn 2)</t>
+          <t>Lịch sử Rinascita (Trích đoạn 2)</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10307,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Lịch Sử Rinascita (Trích Đoạn 3)</t>
+          <t>Lịch sử Rinascita (Trích đoạn 3)</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10377,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Nhật Ký Tu Sĩ của Avenolium Theological Seminary</t>
+          <t>Nhật ký của một Tu Sĩ tại Học viện Thần học Avenolium.</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10447,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Báo Cáo Tóm Tắt Fabricatorium of the Deep (Trích Yếu)</t>
+          <t>Báo Cáo Tóm Tắt Fabricatorium Vực Sâu (Trích Đoạn)</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10517,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Atilius Canyon</t>
+          <t>Hẻm Núi Atilius</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10587,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Hunter's Den</t>
+          <t>Hang ổ Thợ Săn</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10724,7 +10727,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Rustblood Pass</t>
+          <t>Đèo Máu Gỉ</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10934,7 +10937,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>The Wastelands</t>
+          <t>Vùng Đất Hoang Tàn</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11074,7 +11077,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Earthrend Wedge</t>
+          <t>Nêm Đất Nứt</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11147,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Three Heroes' Crest</t>
+          <t>Ba Huy Hiệu Anh Hùng</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11217,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Tideline Verge</t>
+          <t>Bờ Triều Đẫm Máu</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11494,7 +11497,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Maroonwood Crypt</t>
+          <t>Mộ địa Maroonwood</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11567,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Erosion Cavern</t>
+          <t>Hang Động Xói Mòn</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11637,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Howlfang Lair</t>
+          <t>Sào Huyệt Howlfang</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11707,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Sanctum of Quietude</t>
+          <t>Thánh Đường Tĩnh Lặng</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11777,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Maroonwood Maw</t>
+          <t>Hàm Thú Maroonwood</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11847,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Chaos</t>
+          <t>Hỗn Loạn</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11984,7 +11987,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Thử Thách Hàng Tuần: Cơn Đại Họa Cindernite</t>
+          <t>Thử Thách Hàng Tuần: Đại Họa Cindernite</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12057,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Septimont Weather Forecast</t>
+          <t>Dự Báo Thời Tiết Septimont</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12127,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Preparation Area</t>
+          <t>Khu Vực Chuẩn Bị</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12197,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Preparation Area</t>
+          <t>Khu Vực Chuẩn Bị</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12267,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Preparation Area</t>
+          <t>Khu Vực Chuẩn Bị</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12337,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Kho Hàng</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12407,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Cafe Decorator</t>
+          <t>Người Trang Trí Quán Cà Phê</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12477,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Hồ Sơ Vụ Án Namipon</t>
+          <t>Hồ Sơ Bí Mật Namipon</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12547,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Supply Restock</t>
+          <t>Bổ Sung Hàng Tiếp Tế</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12617,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Let's Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12687,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Kho Hàng</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12757,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Cafe Decorator</t>
+          <t>Người Trang Trí Quán Cà Phê</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12827,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Hồ Sơ Vụ Án Namipon</t>
+          <t>Hồ Sơ Bí Mật Namipon</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12897,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Supply Restock</t>
+          <t>Bổ Sung Hàng Tiếp Tế</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12967,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Let's Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13037,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Void Storm Zone I</t>
+          <t>Khu Vực Bão Hư Không I</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13107,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Void Storm Zone II</t>
+          <t>Khu Vực Bão Hư Không II</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13177,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Void Storm Zone III</t>
+          <t>Khu Vực Bão Hư Không III</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13247,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Void Storm Zone IV</t>
+          <t>Khu Vực Bão Hư Không IV</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13317,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Void Storm Zone V</t>
+          <t>Khu Vực Bão Hư Không V</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13387,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Void Storm Zone VI</t>
+          <t>Khu Vực Bão Hư Không VI</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13457,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Void Storm Zone VII</t>
+          <t>Khu Vực Bão Hư Không VII</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13527,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Bề Mặt Frostlands - Khu Void Storm I</t>
+          <t>Bề Mặt Vùng Băng Giá - Khu Vực Bão Hư Không I</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13597,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Bề Mặt Frostlands - Khu Void Storm II</t>
+          <t>Bề Mặt Vùng Đất Băng - Khu Bão Hư Không II</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13667,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Bề Mặt Frostlands - Khu Void Storm III</t>
+          <t>Bề Mặt Vùng Đất Băng - Khu Bão Hư Không III</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13737,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Bề Mặt Frostlands - Khu Void Storm IV</t>
+          <t>Bề Mặt Vùng Đất Băng - Khu Bão Hư Không IV</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13807,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Bề Mặt Frostlands - Zone Void Storm V</t>
+          <t>Bề Mặt Vùng Đất Băng - Khu Bão Hư Không V</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13877,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Dark Tide Conflux</t>
+          <t>Hội Tụ Thủy Triều Bóng Tối</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13947,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Honami City</t>
+          <t>Thành Phố Honami</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14084,7 +14087,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Shashou Cafe</t>
+          <t>Quán Shashou</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14157,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Sazanami Avenue</t>
+          <t>Đại lộ Sazanami</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14227,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Shiawase Fountain Square</t>
+          <t>Quảng trường Đài phun nước Shiawase</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14297,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Meishin Passageway</t>
+          <t>Hành Lang Meishin</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14367,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Hanakage Underground Street</t>
+          <t>Phố Ngầm Hanakage</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14437,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Honami Central Park</t>
+          <t>Công Viên Trung Tâm Honami</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14507,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Sakura Pedway</t>
+          <t>Lối Đi Sakura</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14577,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Sakura Quarter</t>
+          <t>Khu Sakura</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14647,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Harukaze Stadium</t>
+          <t>Sân vận động Harukaze</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14717,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Honami Convention Center</t>
+          <t>Trung tâm Hội nghị Honami</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14854,7 +14857,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Starward Riseway</t>
+          <t>Đại Lộ Sao Chổi</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14927,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Fangspire Chasm</t>
+          <t>Hẻm Núi Nanh Vuốt</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15064,7 +15067,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Stagnant Run</t>
+          <t>Cuộc Chạy Trì Trệ</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15137,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Rebirth Uplands</t>
+          <t>Cao Nguyên Tái Sinh</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15207,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Etching Plains</t>
+          <t>Đồng Bằng Khắc Tạc</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15277,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Startorch Academy</t>
+          <t>Học viện Startorch</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15347,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Mawburrow Desert</t>
+          <t>Sa Mạc Mawburrow</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15417,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Giant's Gaze</t>
+          <t>Ánh Mắt Người Khổng Lồ</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15554,7 +15557,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Spacetrek Collective</t>
+          <t>Tập Đoàn Spacetrek</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15627,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Đường hầm Ngập Nước</t>
+          <t>Đường Hầm Ngập Nước</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15697,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Exospine Barrows</t>
+          <t>Mộ Địa Exospine</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15767,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Emberfall Barrows</t>
+          <t>Mộ Địa Emberfall</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15837,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Riseway-Sundermere Corridor</t>
+          <t>Hành lang Riseway-Sundermere</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15907,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Spacetrek-Bjartr Corridor</t>
+          <t>Hành Lang Spacetrek-Bjartr</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15977,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Dawnsip Fjord</t>
+          <t>Vịnh Bình Minh</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16114,7 +16117,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Soliseed Plains</t>
+          <t>Đồng Bằng Soliseed</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16254,7 +16257,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Solvein Canopy</t>
+          <t>Vòm Solvein</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16327,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Argentflare Drapes</t>
+          <t>Rèm Lửa Bạc</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16397,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Atuja Camp</t>
+          <t>Trại Atuja</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16467,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Jetray Marsh</t>
+          <t>Đầm Lầy Jetray</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16537,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Jetrified Ridge</t>
+          <t>Mỏm Đá Jetray</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16607,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Ribcage Bends</t>
+          <t>Lồng Ngực Cong Oằn</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16677,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Golden Spiral</t>
+          <t>Xoắn Ốc Vàng</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16747,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Lightfall Tunnel</t>
+          <t>Đường Hầm Lightfall</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16817,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Collapsed Arcbend Ravine</t>
+          <t>Hẻm Núi Arcbend Sụp Đổ</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16887,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Voidspawn Control Complex: Sector I</t>
+          <t>Khu Phức Hợp Kiểm Soát Sinh Vật Hư Không: Khu I</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16957,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Voidspawn Control Complex: Sector II</t>
+          <t>Khu Điều Khiển Voidspawn: Khu Vực II</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17027,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Spacetrek Observatory</t>
+          <t>Đài Quan Sát Spacetrek</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17097,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Orbit Valley Pass</t>
+          <t>Đèo Thung Lũng Quỹ Đạo</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17167,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Roya Memorial Park</t>
+          <t>Công Viên Tưởng Niệm Roya</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17237,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Department Vật Chất Hư Không</t>
+          <t>Cục Vật chất Hư không</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17307,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Department Khoa Học Năng Lượng Light</t>
+          <t>Cục Khoa học Năng lượng Ánh sáng</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17377,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Rabelle College</t>
+          <t>Học Viện Rabelle</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17447,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Exo Genesis Labs</t>
+          <t>Phòng Thí Nghiệm Exo Genesis</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17517,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Academy Dormitory</t>
+          <t>Ký Túc Xá Học Viện</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17587,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Living Commons</t>
+          <t>Khu Sinh Hoạt Chung</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17657,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Department Kỹ Thuật Exostrider</t>
+          <t>Cục Kỹ thuật Exostrider</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17727,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Auto Parking &amp; Engineering Xpertise</t>
+          <t>Tự động đỗ xe &amp; Kỹ thuật Xpertise</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17797,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Academia Hall</t>
+          <t>Hội Trường Học Viện</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17867,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Academia Hall</t>
+          <t>Hội Trường Học Viện</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17937,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Synchrolink Training Grounds</t>
+          <t>Bãi Tập Đồng Bộ</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18007,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Express Transfer Station</t>
+          <t>Trạm Trung Chuyển Nhanh</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18077,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>The Solistree's Core</t>
+          <t>Lõi Cây Solistree</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18147,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>First Solistree - 1st Layer</t>
+          <t>Cây Solistree đầu tiên - Tầng 1</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18217,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>First Solistree - 2nd Layer</t>
+          <t>Cây Solistree đầu tiên - Tầng 2</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18287,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>First Solistree - 3rd Layer</t>
+          <t>Cây Solistree đầu tiên - Tầng 3</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18357,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Second Solistree - 1st Layer</t>
+          <t>Cây Solistree - Tầng 1 (Lần 2)</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18427,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Second Solistree - 2nd Layer</t>
+          <t>Cây Solistree - Tầng 2 (Lần 2)</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18497,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Second Solistree - 3rd Layer</t>
+          <t>Cây Solistree - Tầng 3 (Lần 2)</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18567,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Third Solistree - 1st Layer</t>
+          <t>Cây Solistree Thứ Ba - Tầng 1</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18637,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Third Solistree - 2nd Layer</t>
+          <t>Cây Solistree Thứ Ba - Tầng 2</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18707,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Fourth Solistree - 1st Layer</t>
+          <t>Cây Solistree Thứ Tư - Lớp 1</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18777,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Fourth Solistree - 2nd Layer</t>
+          <t>Cây Solistree Thứ Tư - Lớp 2</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18847,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Orbit Valley Pass - Bắc</t>
+          <t>Đèo Thung Lũng Quỹ Đạo - Phía Bắc</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18917,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Orbit Valley Pass - Main</t>
+          <t>Đèo Thung Lũng Quỹ Đạo - Chính Điện</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18987,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Orbit Valley Pass - Nam</t>
+          <t>Đèo Thung Lũng Quỹ Đạo - Phía Nam</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19057,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Riseway-Sundermere Corridor - Underground</t>
+          <t>Hành lang Riseway-Sundermere - Dưới lòng đất</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19127,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Riseway-Sundermere Corridor - Riseway Base</t>
+          <t>Hành lang Riseway-Sundermere - Căn cứ Riseway</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19197,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Spacetrek-Bjartr Corridor</t>
+          <t>Hành Lang Spacetrek-Bjartr</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19267,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Đường hầm Ngập Nước</t>
+          <t>Đường Hầm Ngập Nước</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19337,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Spacetrek Archive - Recreational Zone</t>
+          <t>Lưu Trữ Spacetrek - Khu Giải Trí</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19407,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Quảng trường</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19477,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Teaching Zone</t>
+          <t>Khu Vực Giảng Dạy</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19547,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Freight Zone</t>
+          <t>Khu Vực Hàng Hóa</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19684,7 +19687,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Frostlands Transit Port</t>
+          <t>Trạm Trung Chuyển Vùng Đất Băng</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19757,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Mount Gjallar</t>
+          <t>Thú cưỡi Gjallar</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19827,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Mount Gjallar</t>
+          <t>Thú cưỡi Gjallar</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19897,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Starblind Crashsite</t>
+          <t>Bãi Đổ Nát Starblind</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19967,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Upphaf Forest Ruins</t>
+          <t>Tàn Tích Rừng Upphaf</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20037,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Tidelost Forest</t>
+          <t>Rừng Thủy Triều Lạc Lối</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20107,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Polar Nghiên cứu Outpost</t>
+          <t>Trạm Nghiên Cứu Vùng Cực</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20177,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Roya Icebreak Port</t>
+          <t>Cảng Phá Băng Roya</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20247,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Offshore Void Storm Monitoring Zone</t>
+          <t>Khu Giám Sát Bão Hư Không Ngoài Khơi</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20317,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Ginnungamere Void Storm Monitoring Zone</t>
+          <t>Khu Giám Sát Bão Hư Không Ginnungamere</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20454,7 +20457,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Oldfrost Harbor</t>
+          <t>Bến Cảng Oldfrost</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20594,7 +20597,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Exostrider Observation Station</t>
+          <t>Trạm Quan sát Exostrider</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20667,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Upphaf Forest Excavation Site</t>
+          <t>Địa Điểm Khai Quật Rừng Upphaf</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20737,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Provenance Enclave</t>
+          <t>Khu Bảo Tồn Provenance</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20807,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Upphaf Life Chamber</t>
+          <t>Buồng Sinh Mệnh Upphaf</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20877,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Exostrider Slumber Site</t>
+          <t>Địa điểm Nghỉ Ngơi của Exostrider</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20947,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Wavecleave Cape</t>
+          <t>Áo Choàng Phân Tách Sóng</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21017,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Observation Passage</t>
+          <t>Hồ Sơ Quan Sát</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21087,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>SkyArk Space Station: Khu Phòng Thí Nghiệm I</t>
+          <t>Trạm Không Gian SkyArk: Khu Phòng Thí Nghiệm I</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21157,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>SkyArk Space Station: Khu Phòng Thí Nghiệm II</t>
+          <t>Trạm Vũ Trụ SkyArk: Khu Vực Phòng Thí Nghiệm II</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21227,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>SkyArk Space Station: Blocked Sector</t>
+          <t>Trạm Không Gian SkyArk: Khu Vực Bị Phong Tỏa</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21297,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Everfrost Cavern</t>
+          <t>Hang Đá Everfrost</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21434,7 +21437,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Spacetrek Collective Viện Nghiên Cứu</t>
+          <t>Viện Nghiên Cứu Spacetrek Collective</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21507,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Academy Dormitory</t>
+          <t>Ký Túc Xá Học Viện</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21644,7 +21647,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Lahai-Roi: Người Thu Thập Băng Cuối Cùng</t>
+          <t>Lahai-Roi: Người Thu Thập Cuộn Băng Lời Cuối</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21717,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Monument of Returning Soliseeds</t>
+          <t>Đài Tưởng Niệm Soliseed Trở Về</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21787,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Monument of Returning Soliseeds</t>
+          <t>Đài Tưởng Niệm Soliseed Trở Về</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21857,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Stagnant Run Discord Nest</t>
+          <t>Tổ Tacet Discord Cuộc Chạy Trì Trệ</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21927,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Rebirth Uplands Discord Nest</t>
+          <t>Tổ Tacet Discord Cao Nguyên Tái Sinh</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21997,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Route Constructor: Observatory-Academy Highway</t>
+          <t>Máy Xây Dựng Tuyến Đường: Xa Lộ Đài Thiên Văn - Học Viện</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22067,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Bộ Xây Dựng Tuyến Đường: Đèo Orbit Valley - Phía Bắc</t>
+          <t>Máy Xây Dựng Tuyến Đường: Đèo Thung Lũng Quỹ Đạo - Bắc</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22137,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Bộ Xây Dựng Tuyến Đường: Đèo Orbit Valley - Phía Nam</t>
+          <t>Máy Xây Dựng Tuyến Đường: Đèo Thung Lũng Quỹ Đạo - Nam</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22207,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Route Constructor: Sandreach Passage</t>
+          <t>Máy Xây Dựng Tuyến Đường: Hành Lang Cát Trải</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22277,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Route Constructor: Farer's Road</t>
+          <t>Máy Xây Dựng Tuyến Đường: Con Đường Người Lữ Hành</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22347,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Route Constructor: Sol's Embrace</t>
+          <t>Máy Xây Dựng Tuyến Đường: Vòng Tay Mặt Trời</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22417,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Route Constructor: Starleap Ascent</t>
+          <t>Máy Xây Dựng Tuyến Đường: Con Đường Nhảy Vọt Đến Ngôi Sao</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22487,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Route Constructor: Howling Tunnel</t>
+          <t>Máy Xây Dựng Tuyến Đường: Đường Hầm Gào Thét</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22557,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Route Constructor: Spacetrek–Bjartr Bridge</t>
+          <t>Máy Xây Dựng Tuyến Đường: Cầu Spacetrek–Bjartr</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22627,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Route Constructor: Submerged Tunnel</t>
+          <t>Thợ Xây Dựng Tuyến Đường: Đường Hầm Ngập Nước</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22697,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Spacetrek Observatory</t>
+          <t>Đài Quan Sát Spacetrek</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22767,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Spacetrek Observatory Files</t>
+          <t>Hồ Sơ Đài Quan Sát Spacetrek</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22837,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22907,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22977,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23047,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23117,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23187,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23257,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23327,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23397,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23467,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23537,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23607,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23677,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23747,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23817,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23887,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23957,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24027,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24097,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24167,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24237,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24307,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24377,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24447,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24517,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24587,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24657,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24727,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24797,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot</t>
+          <t>Khởi Động Lại Khối In Thông Minh</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24867,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Route Network Blockage</t>
+          <t>Tắc Nghẽn Mạng Lưới Tuyến Đường</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24937,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Hot Spring Stargazing</t>
+          <t>Ngắm Sao Suối Nước Nóng</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25007,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Motorbike Racing</t>
+          <t>Đua Xe Máy</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25424,7 +25427,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường I</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường I</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25497,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường II</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường II</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25567,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường III</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường III</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25637,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường IV</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường IV</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25707,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường V</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường V</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25777,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường VI</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường VI</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25847,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường VII</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường VII</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25917,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường VIII</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường VIII</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25987,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường IX</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường IX</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26057,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường X</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường X</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26127,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Bộ Xây Dựng Tuyến Đường XI</t>
+          <t>Thử Thách Đua Xe Xây Dựng Tuyến Đường XI</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26197,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Challenge Đua Xe Xây Dựng XII</t>
+          <t>Giải Đua Xây Dựng Tuyến Đường XII</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26267,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Nơi Ánh Sáng Hóa Hình</t>
+          <t>Nơi Ánh Sáng Hình Thành</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26337,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Giai Điệu Lạc Lối</t>
+          <t>Giai Điệu Lạc Khuất</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26407,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Mechascout: Transition</t>
+          <t>Máy trinh sát cơ khí: Transition</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26477,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Treasure Spot: Lahai-Roi</t>
+          <t>Điểm Kho Báu: Lahai-Roi</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26754,7 +26757,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Lightfall Tunnel</t>
+          <t>Đường Hầm Lightfall</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26827,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Riseway-Sundermere Corridor - Riseway Base</t>
+          <t>Hành lang Riseway-Sundermere - Căn cứ Riseway</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26897,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Riseway-Sundermere Corridor - Underground</t>
+          <t>Hành lang Riseway-Sundermere - Dưới lòng đất</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26967,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Spacetrek-Bjartr Corridor</t>
+          <t>Hành Lang Spacetrek-Bjartr</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27037,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Đường hầm Ngập Nước</t>
+          <t>Đường Hầm Ngập Nước</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27107,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>The First Solistree</t>
+          <t>Cây Solistree Đầu Tiên</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27177,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>The Second Solistree</t>
+          <t>Cây Solistree Thứ Hai</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27247,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>The Third Solistree</t>
+          <t>Cây Solistree Thứ Ba</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27317,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>The Fourth Solistree</t>
+          <t>Cây Solistree Thứ Tư</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27454,7 +27457,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Migration Mayhem I</t>
+          <t>Hỗn Loạn Di Cư I</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27527,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Migration Mayhem II</t>
+          <t>Hỗn Loạn Di Cư II</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27597,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Migration Mayhem III</t>
+          <t>Hỗn Loạn Di Cư III</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27667,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Migration Mayhem IV</t>
+          <t>Hỗn Loạn Di Cư IV</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27737,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Migration Mayhem V</t>
+          <t>Hỗn Loạn Di Cư V</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27807,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Migration Mayhem VI</t>
+          <t>Di Cư Hỗn Loạn VI</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27877,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Migration Mayhem VII</t>
+          <t>Di Cư Hỗn Loạn VII</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27947,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Migration Mayhem I (Thường)</t>
+          <t>Hỗn Loạn Di Cư I (Thường)</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28017,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Migration Mayhem II (Thường)</t>
+          <t>Hỗn Loạn Di Cư II (Thường)</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28087,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Migration Mayhem III (Thường)</t>
+          <t>Hỗn Loạn Di Cư III (Thường)</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28157,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Migration Mayhem IV (Thường)</t>
+          <t>Hỗn Loạn Di Cư IV (Thường)</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28227,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Migration Mayhem V (Thường)</t>
+          <t>Di Cư Hỗn Loạn V (Thường)</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28297,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Migration Mayhem VI (Thường)</t>
+          <t>Di Cư Hỗn Loạn VI (Thường)</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28367,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Migration Mayhem VII (Thường)</t>
+          <t>Di Cư Hỗn Loạn VII (Thường)</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28437,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Migration Mayhem I (Khó)</t>
+          <t>Hỗn Loạn Di Cư I (Khó)</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28507,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Migration Mayhem II (Khó)</t>
+          <t>Hỗn Loạn Di Cư II (Khó)</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28577,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Migration Mayhem III (Khó)</t>
+          <t>Hỗn Loạn Di Cư III (Khó)</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28647,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Migration Mayhem IV (Khó)</t>
+          <t>Hỗn Loạn Di Cư IV (Khó)</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28717,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Migration Mayhem V (Khó)</t>
+          <t>Di Cư Hỗn Loạn V (Khó)</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28787,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Migration Mayhem VI (Khó)</t>
+          <t>Di Cư Hỗn Loạn VI (Khó)</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28857,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Migration Mayhem VII (Khó)</t>
+          <t>Di Cư Hỗn Loạn VII (Khó)</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -29134,7 +29137,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Gate of the Lost Star</t>
+          <t>Cổng Ngôi Sao Lạc Lối</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29207,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Weekly Challenge: Gate of the Lost Star</t>
+          <t>Thử Thách Hàng Tuần: Cánh Cổng Ngôi Sao Lạc Lối</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29277,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Seed of Illusory Origin</t>
+          <t>Hạt giống Nguồn Ảo</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29347,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Weekly Challenge: Seed of Illusory Origin</t>
+          <t>Thử Thách Hàng Tuần: Hạt Giống Ảo Ảnh</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29417,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Soliskin Guide</t>
+          <t>Hướng Dẫn Thu Thập Soliskin</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29487,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Smartprint Cube Reboot - Frostland Surface</t>
+          <t>Khởi Động Lại Khối In Thông Minh - Bề Mặt Vùng Đất Băng Giá</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29624,7 +29627,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Nameless Explorer</t>
+          <t>Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29697,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Starblind Crashsite Discord Nest</t>
+          <t>Tổ Tacet Discord tại Bãi Đổ Nát Starblind</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29767,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Rabelle College Entrance</t>
+          <t>Lối Vào Học Viện Rabelle</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29904,7 +29907,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Được Giải Cứu</t>
+          <t>Nhà Nghiên Cứu Được Cứu</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29977,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Miko Ma Yêu Phim</t>
+          <t>Miko Yêu Phim Ảo Mộng</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30047,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Một Mảnh Da Mặt Trời và Người Mysterious Friend</t>
+          <t>Soliskin và Người Bạn Bí Ẩn</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30254,7 +30257,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Everfrost Cavern</t>
+          <t>Hang Đá Everfrost</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30327,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Observation Passage</t>
+          <t>Hồ Sơ Quan Sát</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30397,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Ginnungamere: Byway</t>
+          <t>Ginnungamere: Đường Tắt</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30467,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>SkyArk Space Station: Blocked Sector</t>
+          <t>Trạm Không Gian SkyArk: Khu Vực Bị Phong Tỏa</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30537,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Hy Vọng Tan Băng</t>
+          <t>Hy Vọng Đã Tan Băng</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30607,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Bản Giao Hưởng Băng và Thép</t>
+          <t>Khúc Ca Băng Thép</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30744,7 +30747,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Solisia Landing</t>
+          <t>Bãi Đáp Solisia</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30817,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Sealed Fissure</t>
+          <t>Khe Nứt Đã Niêm Phong</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30887,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Silent Crag</t>
+          <t>Vách Đá Im Lìm</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30957,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Dimmr Deep</t>
+          <t>Vực Sâu Mờ Mịt</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31027,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Stalaglow Cavern</t>
+          <t>Hang Stalaglow</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31097,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Rustbound Hillside</t>
+          <t>Sườn Đồi Gỉ Sét</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31167,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Voidthirst Cradle</t>
+          <t>Cái Nôi Voidthirst</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31237,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Tomorrow's Horizon</t>
+          <t>Bình Minh Ngày Mai</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31307,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Nevermore Halls</t>
+          <t>Đại Sảnh Nevermore</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31377,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Dimmr Plains - Khu Void Storm I</t>
+          <t>Đồng Bằng Dimmr - Vùng Bão Hư Không I</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31447,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Dimmr Plains - Khu Void Storm II</t>
+          <t>Đồng Bằng Dimmr - Vùng Bão Hư Không II</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31517,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Dimmr Plains - Khu Void Storm III</t>
+          <t>Đồng Bằng Dimmr - Vùng Bão Hư Không III</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31587,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Dimmr Plains - Khu Void Storm IV</t>
+          <t>Đồng Bằng Dimmr - Vùng Bão Hư Không IV</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31657,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Voidbane Eldertree - Silent Crag</t>
+          <t>Cây Già Diệt Hư - Vách Núi Tĩnh Lặng</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31727,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Voidbane Eldertree - Sealed Fissure</t>
+          <t>Cây Già Diệt Hư - Khe Nứt Bị Phong Ấn</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31797,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Voidbane Eldertree - Dimmr Deep</t>
+          <t>Cây Già Diệt Hư - Vực Sâu Dimmr</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31867,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Voidbane Eldertree - Solisia Landing</t>
+          <t>Cây Già Diệt Hư - Bãi Đáp Solisia</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31937,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Trại căn cứ</t>
+          <t>Trại Chính</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32007,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo: Ảo Giác Sắc Màu</t>
+          <t>Tổ Tacet Ảo Ảnh: Giấc Mộng Sắc Màu</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32077,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Dimmr Plains Shaft</t>
+          <t>Hầm Đào Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32147,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Trại căn cứ</t>
+          <t>Trại Chính</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32217,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Rustbound Hillside</t>
+          <t>Sườn Đồi Gỉ Sét</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32287,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Twilight Woodlands</t>
+          <t>Rừng Gỗ Hoàng Hôn</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32357,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Stalaglow Cavern</t>
+          <t>Hang Stalaglow</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32427,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Nevermore Halls</t>
+          <t>Đại Sảnh Nevermore</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32497,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Ceased Court</t>
+          <t>Tòa Án Đã Bị Bãi Bỏ</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32567,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Petalfold Recess</t>
+          <t>Khe Hoa Rơi</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32637,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Skyrelic Cascade</t>
+          <t>Thác Tích Trời</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32707,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Voidthirst Cradle</t>
+          <t>Cái Nôi Voidthirst</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32777,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Ljos Isle</t>
+          <t>Đảo Ljos</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32847,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Tomorrow's Horizon</t>
+          <t>Bình Minh Ngày Mai</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32917,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Frostseize Isle</t>
+          <t>Đảo Băng Phong</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32987,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Solvein Heartwood</t>
+          <t>Lòng Gỗ Solvein</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33057,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Monument of Returning Soliseeds</t>
+          <t>Đài Tưởng Niệm Soliseed Trở Về</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33127,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Threat Elimination</t>
+          <t>Loại Bỏ Mối Đe Dọa</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33197,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Light Builder</t>
+          <t>Thợ Xây Ánh Sáng</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33267,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Ngày Hoàn Hảo Để Bay</t>
+          <t>Một Ngày Hoàn Hảo Để Bay Lượn</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33337,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Voidmatter Blocks</t>
+          <t>Khối Vật Chất Hư Không</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33407,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Motorbike - Flight Track 1</t>
+          <t>Xe máy - Đường Bay 1</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33477,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Motorbike - Fixed Track 1</t>
+          <t>Xe máy - Đường ray cố định 1</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33547,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Motorbike - Stunt Track 1</t>
+          <t>Xe máy - Đường Đua Mạo Hiểm 1</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33684,7 +33687,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Survive for 30s</t>
+          <t>Trụ vững trong 30 giây</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33757,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Survive for 30s</t>
+          <t>Trụ vững trong 30 giây</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33827,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Survive for 35s</t>
+          <t>Trụ vững trong 35 giây</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33897,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Survive for 40s</t>
+          <t>Cố gắng trụ vững trong 40 giây</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33967,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Survive for 30s</t>
+          <t>Trụ vững trong 30 giây</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34037,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Survive for 30s</t>
+          <t>Trụ vững trong 30 giây</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34107,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Survive for 60s</t>
+          <t>Cố gắng trụ vững trong 60 giây</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34384,7 +34387,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Trái Tim Dimmr Vỡ Nát</t>
+          <t>Trái Tim Dimmr Vỡ</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34457,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Motorbike - Flight Track 2</t>
+          <t>Xe máy - Đường Bay 2</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34527,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Motorbike - Flight Track 3</t>
+          <t>Xe máy - Đường Bay 3</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34597,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Motorbike - Flight Track 4</t>
+          <t>Xe máy - Đường Bay 4</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34667,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Motorbike - Flight Track 5</t>
+          <t>Xe máy - Đường Bay 5</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34737,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Motorbike - Fixed Track 2</t>
+          <t>Xe máy - Đường Đua Cố Định 2</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34807,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Motorbike - Fixed Track 3</t>
+          <t>Xe máy - Đường Đua Cố Định 3</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34877,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Motorbike - Stunt Track 2</t>
+          <t>Xe máy - Đường Đua Mạo Hiểm 2</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34947,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Voidthirst Cradle - Entrance</t>
+          <t>Cái Nôi Voidthirst - Lối Vào</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35017,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Voidthirst Cradle - First Floor</t>
+          <t>Cái Nôi Voidthirst - Tầng Một</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35087,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Voidthirst Cradle - Second Floor</t>
+          <t>Cái Nôi Voidthirst - Tầng Hai</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35157,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Keystone</t>
+          <t>Đá Chìa Khóa</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35227,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Endreach Barrens</t>
+          <t>Bãi Hoang Endreach</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35434,7 +35437,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>7 Days Sign-in</t>
+          <t>Điểm Danh 7 Ngày</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35507,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Rumbling Hollows</t>
+          <t>Hố Sóng Âm</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
